--- a/unduhan/latihan-22-reservasi-penginapan-soal.xlsx
+++ b/unduhan/latihan-22-reservasi-penginapan-soal.xlsx
@@ -599,7 +599,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Latihan 22 dari 24  |  Tingkat: Menengah  |  Perkiraan waktu: 50 menit  |  pushexcel.github.io/Pushexcel</t>
+          <t>Latihan 22 dari 104  |  Tingkat: Menengah  |  Perkiraan waktu: 50 menit  |  pushexcel.github.io/Pushexcel</t>
         </is>
       </c>
     </row>
